--- a/artfynd/A 24948-2024 artfynd.xlsx
+++ b/artfynd/A 24948-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796440</v>
+        <v>119796442</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>836011</v>
+        <v>836038</v>
       </c>
       <c r="R4" t="n">
-        <v>7431200</v>
+        <v>7431190</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796442</v>
+        <v>119796441</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>836038</v>
+        <v>836036</v>
       </c>
       <c r="R5" t="n">
-        <v>7431190</v>
+        <v>7431180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796441</v>
+        <v>119796440</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>836036</v>
+        <v>836011</v>
       </c>
       <c r="R6" t="n">
-        <v>7431180</v>
+        <v>7431200</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 24948-2024 artfynd.xlsx
+++ b/artfynd/A 24948-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796442</v>
+        <v>119796440</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>836038</v>
+        <v>836011</v>
       </c>
       <c r="R4" t="n">
-        <v>7431190</v>
+        <v>7431200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796440</v>
+        <v>119796442</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>836011</v>
+        <v>836038</v>
       </c>
       <c r="R6" t="n">
-        <v>7431200</v>
+        <v>7431190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 24948-2024 artfynd.xlsx
+++ b/artfynd/A 24948-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796440</v>
+        <v>119796441</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>836011</v>
+        <v>836036</v>
       </c>
       <c r="R4" t="n">
-        <v>7431200</v>
+        <v>7431180</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796441</v>
+        <v>119796442</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>836036</v>
+        <v>836038</v>
       </c>
       <c r="R5" t="n">
-        <v>7431180</v>
+        <v>7431190</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796442</v>
+        <v>119796440</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>836038</v>
+        <v>836011</v>
       </c>
       <c r="R6" t="n">
-        <v>7431190</v>
+        <v>7431200</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 24948-2024 artfynd.xlsx
+++ b/artfynd/A 24948-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796441</v>
+        <v>119796440</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>836036</v>
+        <v>836011</v>
       </c>
       <c r="R4" t="n">
-        <v>7431180</v>
+        <v>7431200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796442</v>
+        <v>119796441</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>836038</v>
+        <v>836036</v>
       </c>
       <c r="R5" t="n">
-        <v>7431190</v>
+        <v>7431180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796440</v>
+        <v>119796442</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>836011</v>
+        <v>836038</v>
       </c>
       <c r="R6" t="n">
-        <v>7431200</v>
+        <v>7431190</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
